--- a/data/trans_dic/IP16A98-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP16A98-Estudios-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -523,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que han  consumido otros medicamentos</t>
+          <t>Menores que han  consumido otros medicamentos (tasa de respuesta: 99,14%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -677,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>5,62; 31,81</t>
+          <t>5,51; 29,16</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>8,42; 44,92</t>
+          <t>7,88; 44,07</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>12,74; 85,36</t>
+          <t>12,36; 89,11</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>9,93; 46,41</t>
+          <t>10,99; 43,6</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 49,11</t>
+          <t>0,0; 47,38</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,92; 40,33</t>
+          <t>4,09; 38,5</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>10,51; 31,8</t>
+          <t>10,07; 30,08</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>8,7; 36,29</t>
+          <t>10,0; 37,78</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>13,33; 64,25</t>
+          <t>13,45; 65,93</t>
         </is>
       </c>
     </row>
@@ -787,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>8,47; 19,91</t>
+          <t>8,6; 20,0</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>11,09; 24,81</t>
+          <t>10,76; 24,37</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6,47; 21,85</t>
+          <t>6,26; 21,75</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>8,82; 20,93</t>
+          <t>9,12; 21,28</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>15,03; 28,87</t>
+          <t>15,04; 29,66</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>13,84; 30,61</t>
+          <t>14,21; 30,86</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,89; 18,29</t>
+          <t>9,99; 18,61</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>14,7; 24,96</t>
+          <t>14,58; 24,35</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>11,45; 23,3</t>
+          <t>12,11; 23,6</t>
         </is>
       </c>
     </row>
@@ -897,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,03; 17,72</t>
+          <t>1,97; 18,08</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4,74; 26,27</t>
+          <t>4,93; 25,41</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>10,24; 30,38</t>
+          <t>10,4; 29,43</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>6,46; 25,28</t>
+          <t>6,39; 26,01</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>8,68; 32,82</t>
+          <t>8,96; 33,5</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5,47; 26,78</t>
+          <t>6,43; 27,87</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>5,87; 18,6</t>
+          <t>5,69; 18,69</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>8,96; 24,48</t>
+          <t>9,16; 25,62</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>10,03; 24,14</t>
+          <t>10,15; 24,13</t>
         </is>
       </c>
     </row>
@@ -1007,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>8,16; 16,92</t>
+          <t>8,11; 16,85</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>11,59; 22,82</t>
+          <t>12,32; 23,02</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>10,46; 27,41</t>
+          <t>11,06; 28,09</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>10,93; 20,32</t>
+          <t>10,71; 20,43</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>14,75; 26,83</t>
+          <t>14,86; 27,45</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>13,19; 25,16</t>
+          <t>13,53; 25,0</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>10,65; 17,31</t>
+          <t>10,81; 17,29</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>14,93; 22,79</t>
+          <t>14,85; 22,65</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>13,66; 24,32</t>
+          <t>13,02; 23,65</t>
         </is>
       </c>
     </row>
@@ -1071,4 +1072,791 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que han  consumido otros medicamentos (tasa de respuesta: 99,14%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="n"/>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Primarios</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>3235</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>3503</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>7699</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>4130</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>1401</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>2701</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>7365</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>4904</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>10399</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>1245; 6586</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>1237; 6915</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>1882; 13571</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>1846; 7327</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>0; 4162</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>641; 6032</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>3968; 11848</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>2447; 9247</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>4154; 20370</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Secundarios</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>11451</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>14309</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>17398</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>14259</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>18422</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>24426</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>25710</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>32732</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>41823</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>7416; 17247</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>8933; 20224</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>7569; 26284</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>9104; 21239</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>12878; 25392</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>17059; 37042</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>18580; 34617</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>24584; 41046</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>29160; 56854</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Universitarios</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>2788</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>3855</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>7646</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>5086</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>5221</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>6390</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>7873</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>9076</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>14036</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>706; 6471</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>1419; 7317</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>4332; 12255</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>2424; 9872</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>2587; 9671</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>2989; 12964</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>4196; 13780</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>5279; 14773</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>8948; 21275</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>17473</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>21668</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>32743</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>23475</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>25045</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>33516</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>40948</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>46712</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>66259</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>11723; 24369</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>15703; 29345</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>19656; 49918</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>16546; 31573</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>18317; 33834</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>24660; 45555</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>32332; 51727</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>37240; 56783</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>46865; 85107</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="C1:E1"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="I1:K1"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP16A98-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP16A98-Estudios-trans_dic.xlsx
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>5,51; 29,16</t>
+          <t>5,61; 29,31</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>7,88; 44,07</t>
+          <t>7,83; 44,81</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>12,36; 89,11</t>
+          <t>12,77; 87,18</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>10,99; 43,6</t>
+          <t>9,23; 43,86</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 47,38</t>
+          <t>0,0; 49,89</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,09; 38,5</t>
+          <t>4,26; 40,48</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>10,07; 30,08</t>
+          <t>9,64; 31,19</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>10,0; 37,78</t>
+          <t>8,26; 34,62</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>13,45; 65,93</t>
+          <t>13,55; 65,09</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>8,6; 20,0</t>
+          <t>8,14; 20,22</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>10,76; 24,37</t>
+          <t>10,64; 24,88</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6,26; 21,75</t>
+          <t>6,75; 22,3</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>9,12; 21,28</t>
+          <t>9,75; 21,55</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>15,04; 29,66</t>
+          <t>15,71; 30,79</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>14,21; 30,86</t>
+          <t>14,35; 31,29</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,99; 18,61</t>
+          <t>10,25; 19,04</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>14,58; 24,35</t>
+          <t>14,9; 24,86</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>12,11; 23,6</t>
+          <t>11,71; 23,39</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,97; 18,08</t>
+          <t>2,08; 18,07</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4,93; 25,41</t>
+          <t>4,4; 25,3</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>10,4; 29,43</t>
+          <t>10,54; 29,95</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>6,39; 26,01</t>
+          <t>5,4; 24,37</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>8,96; 33,5</t>
+          <t>7,62; 33,82</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>6,43; 27,87</t>
+          <t>5,87; 29,09</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>5,69; 18,69</t>
+          <t>5,53; 17,89</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>9,16; 25,62</t>
+          <t>9,76; 25,57</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>10,15; 24,13</t>
+          <t>9,67; 24,21</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>8,11; 16,85</t>
+          <t>8,16; 17,2</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>12,32; 23,02</t>
+          <t>11,96; 23,1</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>11,06; 28,09</t>
+          <t>11,04; 27,62</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>10,71; 20,43</t>
+          <t>10,67; 20,38</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>14,86; 27,45</t>
+          <t>15,43; 27,19</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>13,53; 25,0</t>
+          <t>13,15; 25,49</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>10,81; 17,29</t>
+          <t>10,55; 17,28</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>14,85; 22,65</t>
+          <t>15,13; 23,15</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>13,02; 23,65</t>
+          <t>13,77; 23,99</t>
         </is>
       </c>
     </row>
@@ -1306,47 +1306,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>1245; 6586</t>
+          <t>1267; 6618</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1237; 6915</t>
+          <t>1228; 7031</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1882; 13571</t>
+          <t>1945; 13278</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1846; 7327</t>
+          <t>1551; 7369</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 4162</t>
+          <t>0; 4383</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>641; 6032</t>
+          <t>668; 6342</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>3968; 11848</t>
+          <t>3797; 12284</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>2447; 9247</t>
+          <t>2021; 8474</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>4154; 20370</t>
+          <t>4186; 20110</t>
         </is>
       </c>
     </row>
@@ -1469,47 +1469,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>7416; 17247</t>
+          <t>7017; 17439</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>8933; 20224</t>
+          <t>8829; 20644</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>7569; 26284</t>
+          <t>8156; 26950</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>9104; 21239</t>
+          <t>9731; 21509</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>12878; 25392</t>
+          <t>13449; 26362</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>17059; 37042</t>
+          <t>17229; 37560</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>18580; 34617</t>
+          <t>19073; 35422</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>24584; 41046</t>
+          <t>25114; 41909</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>29160; 56854</t>
+          <t>28196; 56350</t>
         </is>
       </c>
     </row>
@@ -1632,47 +1632,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>706; 6471</t>
+          <t>746; 6467</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1419; 7317</t>
+          <t>1268; 7284</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>4332; 12255</t>
+          <t>4388; 12471</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2424; 9872</t>
+          <t>2048; 9251</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>2587; 9671</t>
+          <t>2199; 9764</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2989; 12964</t>
+          <t>2730; 13528</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>4196; 13780</t>
+          <t>4075; 13193</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>5279; 14773</t>
+          <t>5626; 14746</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>8948; 21275</t>
+          <t>8528; 21341</t>
         </is>
       </c>
     </row>
@@ -1795,47 +1795,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>11723; 24369</t>
+          <t>11808; 24872</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>15703; 29345</t>
+          <t>15240; 29441</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>19656; 49918</t>
+          <t>19615; 49092</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>16546; 31573</t>
+          <t>16488; 31501</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>18317; 33834</t>
+          <t>19022; 33523</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>24660; 45555</t>
+          <t>23963; 46435</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>32332; 51727</t>
+          <t>31577; 51700</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>37240; 56783</t>
+          <t>37927; 58056</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>46865; 85107</t>
+          <t>49549; 86352</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP16A98-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP16A98-Estudios-trans_dic.xlsx
@@ -524,20 +524,20 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que han  consumido otros medicamentos (tasa de respuesta: 99,14%)</t>
+          <t>Menores que consumieron otros medicamentos (tasa de respuesta: 99,14%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -625,32 +625,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>24,58%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>15,95%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>18,21%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>14,33%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>22,32%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>50,55%</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>24,58%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>15,95%</t>
-        </is>
-      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>17,24%</t>
+          <t>24,76%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -665,7 +665,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>33,66%</t>
+          <t>20,91%</t>
         </is>
       </c>
     </row>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>5,61; 29,31</t>
+          <t>9,93; 46,41</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>7,83; 44,81</t>
+          <t>0,0; 49,11</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>12,77; 87,18</t>
+          <t>6,16; 44,01</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>9,23; 43,86</t>
+          <t>5,62; 31,81</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 49,89</t>
+          <t>8,42; 44,92</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,26; 40,48</t>
+          <t>8,28; 50,69</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>9,64; 31,19</t>
+          <t>10,51; 31,8</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>8,26; 34,62</t>
+          <t>8,7; 36,29</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>13,55; 65,09</t>
+          <t>9,01; 37,87</t>
         </is>
       </c>
     </row>
@@ -735,32 +735,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>14,29%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>21,52%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>19,91%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>13,28%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>17,24%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>14,4%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>14,29%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>21,52%</t>
-        </is>
-      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>20,35%</t>
+          <t>18,94%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -775,7 +775,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>17,36%</t>
+          <t>19,46%</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>8,14; 20,22</t>
+          <t>8,82; 20,93</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>10,64; 24,88</t>
+          <t>15,03; 28,87</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6,75; 22,3</t>
+          <t>13,72; 31,89</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>9,75; 21,55</t>
+          <t>8,47; 19,91</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>15,71; 30,79</t>
+          <t>11,09; 24,81</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>14,35; 31,29</t>
+          <t>13,02; 26,23</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>10,25; 19,04</t>
+          <t>9,89; 18,29</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>14,9; 24,86</t>
+          <t>14,7; 24,96</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>11,71; 23,39</t>
+          <t>14,87; 26,15</t>
         </is>
       </c>
     </row>
@@ -845,32 +845,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>13,4%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>18,08%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>14,55%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>7,79%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>13,39%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>18,36%</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>13,4%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>18,08%</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>13,74%</t>
+          <t>19,33%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>15,92%</t>
+          <t>16,86%</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,08; 18,07</t>
+          <t>6,46; 25,28</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4,4; 25,3</t>
+          <t>8,68; 32,82</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>10,54; 29,95</t>
+          <t>5,83; 28,48</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>5,4; 24,37</t>
+          <t>2,03; 17,72</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>7,62; 33,82</t>
+          <t>4,74; 26,27</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5,87; 29,09</t>
+          <t>10,57; 31,5</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>5,53; 17,89</t>
+          <t>5,87; 18,6</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>9,76; 25,57</t>
+          <t>8,96; 24,48</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>9,67; 24,21</t>
+          <t>10,59; 25,36</t>
         </is>
       </c>
     </row>
@@ -955,32 +955,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>15,19%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>20,32%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>18,36%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>12,08%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>17,0%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>18,42%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>15,19%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>20,32%</t>
-        </is>
-      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>18,4%</t>
+          <t>19,45%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -995,7 +995,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>18,41%</t>
+          <t>18,87%</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>8,16; 17,2</t>
+          <t>10,93; 20,32</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>11,96; 23,1</t>
+          <t>14,75; 26,83</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>11,04; 27,62</t>
+          <t>13,24; 25,92</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>10,67; 20,38</t>
+          <t>8,16; 16,92</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>15,43; 27,19</t>
+          <t>11,59; 22,82</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>13,15; 25,49</t>
+          <t>14,25; 24,8</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>10,55; 17,28</t>
+          <t>10,65; 17,31</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>15,13; 23,15</t>
+          <t>14,93; 22,79</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>13,77; 23,99</t>
+          <t>15,03; 23,36</t>
         </is>
       </c>
     </row>
@@ -1099,20 +1099,20 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que han  consumido otros medicamentos (tasa de respuesta: 99,14%)</t>
+          <t>Menores que consumieron otros medicamentos (tasa de respuesta: 99,14%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -1200,27 +1200,27 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>5</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -1253,32 +1253,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>4130</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>1401</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>2535</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
           <t>3235</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>3503</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>7699</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>4130</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>1401</t>
-        </is>
-      </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2701</t>
+          <t>2422</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -1293,7 +1293,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>10399</t>
+          <t>4957</t>
         </is>
       </c>
     </row>
@@ -1306,47 +1306,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>1267; 6618</t>
+          <t>1668; 7799</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1228; 7031</t>
+          <t>0; 4314</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1945; 13278</t>
+          <t>857; 6126</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1551; 7369</t>
+          <t>1268; 7184</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 4383</t>
+          <t>1321; 7048</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>668; 6342</t>
+          <t>809; 4958</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>3797; 12284</t>
+          <t>4141; 12525</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>2021; 8474</t>
+          <t>2130; 8883</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>4186; 20110</t>
+          <t>2136; 8975</t>
         </is>
       </c>
     </row>
@@ -1363,32 +1363,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
           <t>17</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>26</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>31</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -1416,32 +1416,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>14259</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>18422</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>21483</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>11451</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>14309</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>17398</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>14259</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>18422</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>24426</t>
+          <t>17558</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>41823</t>
+          <t>39041</t>
         </is>
       </c>
     </row>
@@ -1469,47 +1469,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>7017; 17439</t>
+          <t>8806; 20884</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>8829; 20644</t>
+          <t>12867; 24714</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>8156; 26950</t>
+          <t>14803; 34418</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>9731; 21509</t>
+          <t>7307; 17174</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>13449; 26362</t>
+          <t>9205; 20590</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>17229; 37560</t>
+          <t>12065; 24311</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>19073; 35422</t>
+          <t>18405; 34023</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>25114; 41909</t>
+          <t>24788; 42082</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>28196; 56350</t>
+          <t>29838; 52456</t>
         </is>
       </c>
     </row>
@@ -1526,32 +1526,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>13</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1579,32 +1579,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>5086</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>5221</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>6275</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
           <t>2788</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr">
         <is>
           <t>3855</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>7646</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>5086</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>5221</t>
-        </is>
-      </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>6390</t>
+          <t>7832</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>14036</t>
+          <t>14107</t>
         </is>
       </c>
     </row>
@@ -1632,47 +1632,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>746; 6467</t>
+          <t>2452; 9596</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1268; 7284</t>
+          <t>2507; 9474</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>4388; 12471</t>
+          <t>2513; 12279</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2048; 9251</t>
+          <t>725; 6344</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>2199; 9764</t>
+          <t>1365; 7563</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2730; 13528</t>
+          <t>4285; 12765</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>4075; 13193</t>
+          <t>4327; 13716</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>5626; 14746</t>
+          <t>5167; 14116</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>8528; 21341</t>
+          <t>8855; 21210</t>
         </is>
       </c>
     </row>
@@ -1689,32 +1689,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
           <t>26</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr">
         <is>
           <t>32</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>43</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>42</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1742,32 +1742,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>23475</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>25045</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>30293</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>17473</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>21668</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>32743</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>23475</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>25045</t>
-        </is>
-      </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>33516</t>
+          <t>27812</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1782,7 +1782,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>66259</t>
+          <t>58105</t>
         </is>
       </c>
     </row>
@@ -1795,47 +1795,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>11808; 24872</t>
+          <t>16896; 31398</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>15240; 29441</t>
+          <t>18186; 33081</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>19615; 49092</t>
+          <t>21832; 42758</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>16488; 31501</t>
+          <t>11807; 24464</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>19022; 33523</t>
+          <t>14773; 29092</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>23963; 46435</t>
+          <t>20372; 35456</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>31577; 51700</t>
+          <t>31850; 51779</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>37927; 58056</t>
+          <t>37429; 57146</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>49549; 86352</t>
+          <t>46288; 71920</t>
         </is>
       </c>
     </row>
